--- a/astro-site/public/dl/pizza-shop-checklist-templates/06-pizza-shop-event-checklists.xlsx
+++ b/astro-site/public/dl/pizza-shop-checklist-templates/06-pizza-shop-event-checklists.xlsx
@@ -1092,9 +1092,9 @@
       <c r="A14" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="26" t="inlineStr">
-        <is>
-          <t>Turn on the delivery apps early</t>
+      <c r="B14" s="33" t="inlineStr">
+        <is>
+          <t>Check every delivery app is live and set longer prep times for the rush</t>
         </is>
       </c>
       <c r="C14" s="27" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="E14" s="27" t="inlineStr">
         <is>
-          <t>5:00 PM</t>
+          <t>2 h before kickoff</t>
         </is>
       </c>
       <c r="F14" s="28" t="n"/>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="E12" s="27" t="inlineStr">
         <is>
-          <t>15 days out</t>
+          <t>2 weeks out</t>
         </is>
       </c>
       <c r="F12" s="28" t="n"/>
